--- a/artfynd/A 33826-2024 artfynd.xlsx
+++ b/artfynd/A 33826-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747232</v>
       </c>
       <c r="B2" t="n">
-        <v>92221</v>
+        <v>92225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122747233</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>91354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 33826-2024 artfynd.xlsx
+++ b/artfynd/A 33826-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747232</v>
+        <v>122747233</v>
       </c>
       <c r="B2" t="n">
-        <v>92225</v>
+        <v>91354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612954</v>
+        <v>613033</v>
       </c>
       <c r="R2" t="n">
-        <v>6561420</v>
+        <v>6561430</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747233</v>
+        <v>122747232</v>
       </c>
       <c r="B3" t="n">
-        <v>91354</v>
+        <v>92225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613033</v>
+        <v>612954</v>
       </c>
       <c r="R3" t="n">
-        <v>6561430</v>
+        <v>6561420</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 33826-2024 artfynd.xlsx
+++ b/artfynd/A 33826-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747233</v>
+        <v>122747232</v>
       </c>
       <c r="B2" t="n">
-        <v>91354</v>
+        <v>92225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613033</v>
+        <v>612954</v>
       </c>
       <c r="R2" t="n">
-        <v>6561430</v>
+        <v>6561420</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747232</v>
+        <v>122747233</v>
       </c>
       <c r="B3" t="n">
-        <v>92225</v>
+        <v>91354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612954</v>
+        <v>613033</v>
       </c>
       <c r="R3" t="n">
-        <v>6561420</v>
+        <v>6561430</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 33826-2024 artfynd.xlsx
+++ b/artfynd/A 33826-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747232</v>
+        <v>122747233</v>
       </c>
       <c r="B2" t="n">
-        <v>92225</v>
+        <v>91362</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612954</v>
+        <v>613033</v>
       </c>
       <c r="R2" t="n">
-        <v>6561420</v>
+        <v>6561430</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747233</v>
+        <v>122747232</v>
       </c>
       <c r="B3" t="n">
-        <v>91354</v>
+        <v>92233</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613033</v>
+        <v>612954</v>
       </c>
       <c r="R3" t="n">
-        <v>6561430</v>
+        <v>6561420</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 33826-2024 artfynd.xlsx
+++ b/artfynd/A 33826-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747233</v>
+        <v>122747232</v>
       </c>
       <c r="B2" t="n">
-        <v>91362</v>
+        <v>92233</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613033</v>
+        <v>612954</v>
       </c>
       <c r="R2" t="n">
-        <v>6561430</v>
+        <v>6561420</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747232</v>
+        <v>122747233</v>
       </c>
       <c r="B3" t="n">
-        <v>92233</v>
+        <v>91362</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612954</v>
+        <v>613033</v>
       </c>
       <c r="R3" t="n">
-        <v>6561420</v>
+        <v>6561430</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 33826-2024 artfynd.xlsx
+++ b/artfynd/A 33826-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747232</v>
+        <v>122747233</v>
       </c>
       <c r="B2" t="n">
-        <v>92233</v>
+        <v>91365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612954</v>
+        <v>613033</v>
       </c>
       <c r="R2" t="n">
-        <v>6561420</v>
+        <v>6561430</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747233</v>
+        <v>122747232</v>
       </c>
       <c r="B3" t="n">
-        <v>91362</v>
+        <v>92236</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613033</v>
+        <v>612954</v>
       </c>
       <c r="R3" t="n">
-        <v>6561430</v>
+        <v>6561420</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 33826-2024 artfynd.xlsx
+++ b/artfynd/A 33826-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747233</v>
       </c>
       <c r="B2" t="n">
-        <v>91365</v>
+        <v>91367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122747232</v>
       </c>
       <c r="B3" t="n">
-        <v>92236</v>
+        <v>92238</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 33826-2024 artfynd.xlsx
+++ b/artfynd/A 33826-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747233</v>
+        <v>122747232</v>
       </c>
       <c r="B2" t="n">
-        <v>91367</v>
+        <v>92238</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613033</v>
+        <v>612954</v>
       </c>
       <c r="R2" t="n">
-        <v>6561430</v>
+        <v>6561420</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747232</v>
+        <v>122747233</v>
       </c>
       <c r="B3" t="n">
-        <v>92238</v>
+        <v>91367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612954</v>
+        <v>613033</v>
       </c>
       <c r="R3" t="n">
-        <v>6561420</v>
+        <v>6561430</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
